--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rd68b94456e794b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rf40319cb1ec34649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R0d1fc6fa0913497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R808251f7c58b4764"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R167488f0775b4807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R84e61513b4b449e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R3000ad79fc774086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rd13e877614d24770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R85d01b989d464ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra3d8d6e835564fcc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -767,7 +767,7 @@
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>playwright.config.ts,tests/support_console_realtime.spec.ts,reports/case_results.csv,reports/socket_event_audit.csv,reports/focus_path.csv,artifacts/agent-billing-after-feed.png</x:v>
@@ -776,7 +776,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>交付物答案清单</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
